--- a/03_Outputs/Cartama/05_Economia/economia.xlsx
+++ b/03_Outputs/Cartama/05_Economia/economia.xlsx
@@ -12812,10 +12812,8 @@
       <c r="F5" s="118">
         <v>10.2338401030599</v>
       </c>
-      <c r="G5" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G5" s="120">
+        <v>0.0180048952400001</v>
       </c>
       <c r="H5" s="122">
         <v>9.85954466335001</v>
@@ -13289,7 +13287,7 @@
         <v>414.398833617597</v>
       </c>
       <c r="G13" s="121">
-        <v>4.46978427471002</v>
+        <v>4.48778916995002</v>
       </c>
       <c r="H13" s="123">
         <v>99.4809769753501</v>
@@ -15713,10 +15711,8 @@
       <c r="F54" s="118">
         <v>13.3672458754331</v>
       </c>
-      <c r="G54" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G54" s="120">
+        <v>0.00834872688568909</v>
       </c>
       <c r="H54" s="122">
         <v>6.46876150819251</v>
@@ -16131,7 +16127,7 @@
         <v>488.894416204276</v>
       </c>
       <c r="G61" s="121">
-        <v>14.4425017023248</v>
+        <v>14.4508504292105</v>
       </c>
       <c r="H61" s="123">
         <v>66.3498873041848</v>
@@ -17963,10 +17959,8 @@
       <c r="F92" s="118">
         <v>75.4923303050864</v>
       </c>
-      <c r="G92" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G92" s="120">
+        <v>0.0318665779664319</v>
       </c>
       <c r="H92" s="122">
         <v>10.9116786367956</v>
@@ -18263,7 +18257,7 @@
         <v>602.462114083868</v>
       </c>
       <c r="G97" s="121">
-        <v>30.6566529154785</v>
+        <v>30.688519493445</v>
       </c>
       <c r="H97" s="123">
         <v>64.6858955783671</v>
@@ -18675,10 +18669,8 @@
       <c r="F104" s="118">
         <v>82.2420226815805</v>
       </c>
-      <c r="G104" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G104" s="120">
+        <v>0.0697066901043137</v>
       </c>
       <c r="H104" s="122">
         <v>8.11187848586589</v>
@@ -18975,7 +18967,7 @@
         <v>655.856996122754</v>
       </c>
       <c r="G109" s="121">
-        <v>22.7971716887446</v>
+        <v>22.8668783788489</v>
       </c>
       <c r="H109" s="123">
         <v>81.1089438518604</v>
@@ -19387,10 +19379,8 @@
       <c r="F116" s="118">
         <v>87.3022476986768</v>
       </c>
-      <c r="G116" s="120" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="G116" s="120">
+        <v>0.0741593673521075</v>
       </c>
       <c r="H116" s="122">
         <v>7.2053287082748</v>
@@ -19687,7 +19677,7 @@
         <v>701.624646326197</v>
       </c>
       <c r="G121" s="121">
-        <v>17.6310483294329</v>
+        <v>17.705207696785</v>
       </c>
       <c r="H121" s="123">
         <v>73.9796105962778</v>
@@ -23109,7 +23099,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>17.6310483294329</v>
+        <v>17.705207696785</v>
       </c>
     </row>
     <row r="4">
